--- a/artfynd/A 64124-2025 artfynd.xlsx
+++ b/artfynd/A 64124-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,51 +675,50 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>111371885</v>
+        <v>111371491</v>
       </c>
       <c r="B2" t="n">
-        <v>96348</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Borlänge (Borlänge), Dlr</t>
+          <t>Borlänge, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>532097.1635129997</v>
+        <v>532177</v>
       </c>
       <c r="R2" t="n">
-        <v>6709323.289677891</v>
+        <v>6709267</v>
       </c>
       <c r="S2" t="n">
         <v>20</v>
@@ -749,19 +748,9 @@
           <t>2023-08-09</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2023-08-09</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -788,54 +777,51 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>111371673</v>
+        <v>112503388</v>
       </c>
       <c r="B3" t="n">
-        <v>96348</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Borlänge (Borlänge), Dlr</t>
+          <t>Nedanför Kolmossen, Nedanför Kolmossen, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>532141.017279049</v>
+        <v>532092</v>
       </c>
       <c r="R3" t="n">
-        <v>6709328.111239178</v>
+        <v>6709321</v>
       </c>
       <c r="S3" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -859,22 +845,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-08-09</t>
+          <t>2023-10-03</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-08-09</t>
+          <t>2023-10-03</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -883,72 +869,70 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Niklas Rehn</t>
+          <t>Holger Martinussen</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Niklas Rehn</t>
+          <t>Holger Martinussen, Niklas Rehn</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>111371751</v>
+        <v>112503280</v>
       </c>
       <c r="B4" t="n">
-        <v>89845</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Borlänge (Borlänge), Dlr</t>
+          <t>Nedanför Kolmossen, Nedanför Kolmossen, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>532110.0912517949</v>
+        <v>532092</v>
       </c>
       <c r="R4" t="n">
-        <v>6709311.586508158</v>
+        <v>6709321</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -972,22 +956,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2023-08-09</t>
+          <t>2023-10-03</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2023-08-09</t>
+          <t>2023-10-03</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,37 +980,33 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Niklas Rehn</t>
+          <t>Holger Martinussen</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Niklas Rehn</t>
+          <t>Holger Martinussen, Niklas Rehn</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>111371810</v>
+        <v>111371751</v>
       </c>
       <c r="B5" t="n">
-        <v>89845</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1039,26 +1019,26 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Borlänge (Borlänge), Dlr</t>
+          <t>Borlänge, Borlänge, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>532100.306316702</v>
+        <v>532110</v>
       </c>
       <c r="R5" t="n">
-        <v>6709302.636023568</v>
+        <v>6709311</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1088,19 +1068,9 @@
           <t>2023-08-09</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2023-08-09</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1127,15 +1097,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>111371491</v>
+        <v>111371810</v>
       </c>
       <c r="B6" t="n">
-        <v>89686</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1143,39 +1108,35 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>658</v>
+        <v>1209</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Borlänge, Dlr</t>
+          <t>Borlänge, Borlänge, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>532177.0700080059</v>
+        <v>532100</v>
       </c>
       <c r="R6" t="n">
-        <v>6709267.371944865</v>
+        <v>6709302</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1205,19 +1166,9 @@
           <t>2023-08-09</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2023-08-09</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1247,16 +1198,11 @@
         <v>112503272</v>
       </c>
       <c r="B7" t="n">
-        <v>90101</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1269,12 +1215,12 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1283,14 +1229,14 @@
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Nedanför Kolmossen (Nedanför Kolmossen), Dlr</t>
+          <t>Nedanför Kolmossen, Nedanför Kolmossen, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
         <v>532092</v>
       </c>
       <c r="R7" t="n">
-        <v>6709320</v>
+        <v>6709321</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1360,56 +1306,49 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>112503280</v>
+        <v>111371530</v>
       </c>
       <c r="B8" t="n">
-        <v>89661</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Nedanför Kolmossen (Nedanför Kolmossen), Dlr</t>
+          <t>Borlänge, Borlänge, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>532092</v>
+        <v>532183</v>
       </c>
       <c r="R8" t="n">
-        <v>6709320</v>
+        <v>6709297</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1433,22 +1372,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2023-10-03</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>17:05</t>
+          <t>2023-08-09</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2023-10-03</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>17:05</t>
+          <t>2023-08-09</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1457,75 +1386,67 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Holger Martinussen</t>
+          <t>Niklas Rehn</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Holger Martinussen, Niklas Rehn</t>
+          <t>Niklas Rehn</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>112503388</v>
+        <v>111371673</v>
       </c>
       <c r="B9" t="n">
-        <v>89942</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Nedanför Kolmossen (Nedanför Kolmossen), Dlr</t>
+          <t>Borlänge, Borlänge, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>532092</v>
+        <v>532142</v>
       </c>
       <c r="R9" t="n">
-        <v>6709320</v>
+        <v>6709328</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1549,22 +1470,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2023-10-03</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>17:05</t>
+          <t>2023-08-09</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2023-10-03</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>17:05</t>
+          <t>2023-08-09</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1573,22 +1484,119 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Holger Martinussen</t>
+          <t>Niklas Rehn</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Holger Martinussen, Niklas Rehn</t>
+          <t>Niklas Rehn</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>111371885</v>
+      </c>
+      <c r="B10" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Borlänge, Borlänge, Dlr</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>532098</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6709323</v>
+      </c>
+      <c r="S10" t="n">
+        <v>20</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Torsång</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2023-08-09</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2023-08-09</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Niklas Rehn</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Niklas Rehn</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 64124-2025 artfynd.xlsx
+++ b/artfynd/A 64124-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AZ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -783,6 +788,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112503388</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -894,6 +904,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112503280</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -992,6 +1007,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111371751</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1090,6 +1110,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111371810</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1201,6 +1226,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112503272</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1299,6 +1329,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111371673</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1397,6 +1432,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111371885</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1499,6 +1539,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111371491</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1597,8 +1642,24 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111371530</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>